--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -624,12 +624,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -659,12 +659,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -694,13 +694,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -769,13 +769,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰</t>
+          <t xml:space="preserve">潢|–汰</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -919,13 +919,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -998,13 +998,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㳞</t>
+          <t xml:space="preserve">潢|–㳞</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1448,13 +1448,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1602,13 +1602,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―無</t>
+          <t xml:space="preserve">汰|–無</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1677,13 +1677,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1752,13 +1752,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1897,13 +1897,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1972,13 +1972,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰</t>
+          <t xml:space="preserve">潢|–汰</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2205,13 +2205,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㳞</t>
+          <t xml:space="preserve">潢|–㳞</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I53" s="2"/>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2664,13 +2664,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 또는 짧은 ―</t>
+          <t xml:space="preserve">· 또는 짧은 –</t>
         </is>
       </c>
       <c r="K59" s="2"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無 앞 ― 없음(줄 2와 다름)</t>
+          <t xml:space="preserve">無 앞 – 없음(줄 2와 다름)</t>
         </is>
       </c>
       <c r="K62" s="2"/>
@@ -2897,13 +2897,13 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3006,7 +3006,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -3059,7 +3059,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="9"/>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="9"/>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="9"/>
@@ -3105,25 +3105,25 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="10"/>
@@ -3144,7 +3144,7 @@
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -3166,7 +3166,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
@@ -3191,7 +3191,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="9"/>
@@ -3218,7 +3218,7 @@
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -3240,7 +3240,7 @@
       <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -3281,7 +3281,7 @@
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3303,7 +3303,7 @@
       <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -3349,7 +3349,7 @@
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="9"/>
@@ -3392,7 +3392,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -3456,7 +3456,7 @@
       <c r="D15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -3467,14 +3467,14 @@
       <c r="F15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       <c r="B17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3541,7 +3541,7 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -3571,7 +3571,7 @@
       <c r="C18" s="10"/>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2977,61 +3018,61 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">박연폭포</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">범</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">박연</t>
         </is>
@@ -3039,137 +3080,137 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">김가</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="25"/>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="26"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="26"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="26"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">디여</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">정으</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">폭</t>
         </is>
@@ -3177,73 +3218,73 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">포</t>
         </is>
@@ -3251,73 +3292,73 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢‹</t>
         </is>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에두</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">흘러</t>
         </is>
@@ -3325,77 +3366,77 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="28"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞潢</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">내리</t>
         </is>
@@ -3403,38 +3444,38 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -3442,42 +3483,42 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">쫑</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –無</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="24"/>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
@@ -3485,77 +3526,77 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3563,31 +3604,31 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="26"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="26"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="26"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -3003,20 +3003,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       <c r="C4" s="25"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="25"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="I6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       <c r="C8" s="25"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="25"/>
@@ -3238,12 +3238,12 @@
       <c r="G8" s="25"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="I10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3364,11 +3364,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="28"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G12" s="25"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="I12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -2666,12 +2666,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I57" s="3"/>
@@ -3294,7 +3294,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C10" s="27"/>

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -3074,7 +3074,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">박연</t>
+          <t xml:space="preserve">박
+연</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3116,8 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">김가</t>
+          <t xml:space="preserve">김
+가</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -3179,7 +3181,8 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">디여</t>
+          <t xml:space="preserve">디
+여</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -3201,7 +3204,8 @@
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">정으</t>
+          <t xml:space="preserve">정
+으</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -3338,7 +3342,8 @@
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">에두</t>
+          <t xml:space="preserve">에
+두</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -3360,7 +3365,8 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">흘러</t>
+          <t xml:space="preserve">흘
+러</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3444,8 @@
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">내리</t>
+          <t xml:space="preserve">내
+리</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3039,7 +3062,7 @@
 南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3050,7 +3073,7 @@
 –</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3061,7 +3084,7 @@
 南</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">범</t>
         </is>
@@ -3072,7 +3095,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">박
 연</t>
@@ -3086,25 +3109,25 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -3114,7 +3137,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">김
 가</t>
@@ -3125,14 +3148,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3142,7 +3165,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="25"/>
+      <c r="I5" s="31"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -3151,25 +3174,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="26"/>
+      <c r="I6" s="32"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -3179,7 +3202,7 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디
 여</t>
@@ -3191,7 +3214,7 @@
 –</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3202,7 +3225,7 @@
 南</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">정
 으</t>
@@ -3214,7 +3237,7 @@
 –</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">폭</t>
         </is>
@@ -3227,25 +3250,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="25"/>
+      <c r="I8" s="31"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -3255,7 +3278,7 @@
 汰</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3266,7 +3289,7 @@
 –汰</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3277,7 +3300,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -3288,7 +3311,7 @@
 –汰</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">포</t>
         </is>
@@ -3301,25 +3324,25 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -3329,7 +3352,7 @@
 –</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -3340,7 +3363,7 @@
 無</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 두</t>
@@ -3352,7 +3375,7 @@
 –</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
@@ -3363,7 +3386,7 @@
 南</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">흘
 러</t>
@@ -3377,13 +3400,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3393,13 +3416,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="25"/>
+      <c r="I12" s="31"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -3409,7 +3432,7 @@
 㳞潢</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3420,7 +3443,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -3431,7 +3454,7 @@
 㳞潢</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
@@ -3442,7 +3465,7 @@
 –南</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">내
 리</t>
@@ -3456,13 +3479,13 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3472,7 +3495,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3482,7 +3505,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -3496,7 +3519,7 @@
 無</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -3507,7 +3530,7 @@
 –㳞</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">쫑</t>
         </is>
@@ -3518,14 +3541,14 @@
 –無</t>
         </is>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
@@ -3538,19 +3561,19 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E16" s="25"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -3560,7 +3583,7 @@
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I16" s="25"/>
+      <c r="I16" s="31"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
@@ -3570,7 +3593,7 @@
 –</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3581,7 +3604,7 @@
 南</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3592,7 +3615,7 @@
 –</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3603,7 +3626,7 @@
 南</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3616,26 +3639,26 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="26"/>
+      <c r="I18" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -721,10 +721,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -398,46 +398,14 @@
     <t xml:space="preserve">南 덧써 고친 흔적</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">㴌
+–
 –</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+  </si>
+  <si>
+    <t xml:space="preserve">㴌
 㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">박
@@ -456,54 +424,14 @@
 으</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">無
 汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+㴌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㴌
+–汰
+㴌</t>
   </si>
   <si>
     <t xml:space="preserve">에
@@ -515,63 +443,14 @@
 러</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+    <t xml:space="preserve">㴌
+㳞㴌
+無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無
+㴌
 㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">종
@@ -582,25 +461,9 @@
 아</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">無
 –南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+㴌</t>
   </si>
   <si>
     <t xml:space="preserve">내
@@ -608,42 +471,9 @@
 는</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–㳞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">㴌
+–㳞
+㴌汰</t>
   </si>
 </sst>
 </file>
@@ -662,17 +492,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -794,7 +624,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -848,6 +678,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2302,236 +2172,236 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="52.63" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="9" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="18" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B8" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="20" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B9" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B10" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="21" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2541,7 +2411,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/박연폭포 (느리게).xlsx
+++ b/sheets/민요/검수/박연폭포 (느리게).xlsx
@@ -2178,13 +2178,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
   </cols>
   <sheetData>
